--- a/filer/35954716_salling_group_a_s.xlsx
+++ b/filer/35954716_salling_group_a_s.xlsx
@@ -7454,7 +7454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7681,22 +7681,22 @@
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:OtherRevenue</t>
+          <t>ifrs-full:ProceedsFromSalesOrMaturityOfFinancialInstrumentsClassifiedAsInvestingActivities</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:OtherRevenue</t>
+          <t>ifrs-full:ProceedsFromSalesOrMaturityOfFinancialInstrumentsClassifiedAsInvestingActivities</t>
         </is>
       </c>
       <c r="D8" s="38" t="n"/>
       <c r="E8" s="38" t="n"/>
       <c r="F8" s="38" t="n"/>
       <c r="G8" s="38" t="n">
-        <v>560000</v>
+        <v>186000</v>
       </c>
       <c r="H8" s="38" t="n">
-        <v>730000</v>
+        <v>334000</v>
       </c>
       <c r="I8" s="39" t="inlineStr">
         <is>
@@ -7712,22 +7712,22 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:ProceedsFromSalesOrMaturityOfFinancialInstrumentsClassifiedAsInvestingActivities</t>
+          <t>ifrs-full:PurchaseOfInvestmentProperty</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:ProceedsFromSalesOrMaturityOfFinancialInstrumentsClassifiedAsInvestingActivities</t>
+          <t>ifrs-full:PurchaseOfInvestmentProperty</t>
         </is>
       </c>
       <c r="D9" s="35" t="n"/>
       <c r="E9" s="35" t="n"/>
       <c r="F9" s="35" t="n"/>
       <c r="G9" s="35" t="n">
-        <v>186000</v>
+        <v>7000</v>
       </c>
       <c r="H9" s="35" t="n">
-        <v>334000</v>
+        <v>9000</v>
       </c>
       <c r="I9" s="36" t="inlineStr">
         <is>
@@ -7743,22 +7743,22 @@
       </c>
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:PurchaseOfInvestmentProperty</t>
+          <t>ifrs-full:ReclassificationAdjustmentsOnCashFlowHedgesNetOfTax</t>
         </is>
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:PurchaseOfInvestmentProperty</t>
+          <t>ifrs-full:ReclassificationAdjustmentsOnCashFlowHedgesNetOfTax</t>
         </is>
       </c>
       <c r="D10" s="38" t="n"/>
       <c r="E10" s="38" t="n"/>
       <c r="F10" s="38" t="n"/>
       <c r="G10" s="38" t="n">
-        <v>7000</v>
+        <v>59000</v>
       </c>
       <c r="H10" s="38" t="n">
-        <v>9000</v>
+        <v>-1000</v>
       </c>
       <c r="I10" s="39" t="inlineStr">
         <is>
@@ -7774,86 +7774,24 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:ReclassificationAdjustmentsOnCashFlowHedgesNetOfTax</t>
+          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:ReclassificationAdjustmentsOnCashFlowHedgesNetOfTax</t>
+          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
         </is>
       </c>
       <c r="D11" s="35" t="n"/>
       <c r="E11" s="35" t="n"/>
       <c r="F11" s="35" t="n"/>
       <c r="G11" s="35" t="n">
-        <v>59000</v>
+        <v>239000</v>
       </c>
       <c r="H11" s="35" t="n">
-        <v>-1000</v>
+        <v>317000</v>
       </c>
       <c r="I11" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B12" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
-        </is>
-      </c>
-      <c r="C12" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:ReserveOfExchangeDifferencesOnTranslation</t>
-        </is>
-      </c>
-      <c r="D12" s="38" t="n"/>
-      <c r="E12" s="38" t="n"/>
-      <c r="F12" s="38" t="n"/>
-      <c r="G12" s="38" t="n">
-        <v>239000</v>
-      </c>
-      <c r="H12" s="38" t="n">
-        <v>317000</v>
-      </c>
-      <c r="I12" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:RevenueFromSaleOfGoods</t>
-        </is>
-      </c>
-      <c r="C13" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:RevenueFromSaleOfGoods</t>
-        </is>
-      </c>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n">
-        <v>71616000</v>
-      </c>
-      <c r="H13" s="35" t="n">
-        <v>82438000</v>
-      </c>
-      <c r="I13" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>
